--- a/data/internalStats2/File1/RPT_RPT8107702707903CZ_internalStats2.xlsx
+++ b/data/internalStats2/File1/RPT_RPT8107702707903CZ_internalStats2.xlsx
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="Z25" s="72" t="n">
-        <v>4.172186264642537</v>
+        <v>3.33774901171403</v>
       </c>
       <c r="AA25" s="180" t="n">
         <v>0.002658168184929212</v>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="Z121" s="72" t="n">
-        <v>4.172186264642537</v>
+        <v>3.33774901171403</v>
       </c>
       <c r="AA121" s="180" t="n">
         <v>0.3863903738861535</v>
